--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run10/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run10/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9685,0.0149,0.0074,0.0029</t>
-  </si>
-  <si>
-    <t>0.0297,0.0011,0.0004,0.9917</t>
-  </si>
-  <si>
-    <t>0.9356,0.0071,0.0017,0.0568</t>
-  </si>
-  <si>
-    <t>0.0234,0.0029,0.0038,0.9867</t>
-  </si>
-  <si>
-    <t>0.9977,0.0006,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9933,0.0014,0.0004,0.0039</t>
-  </si>
-  <si>
-    <t>0.9955,0.0018,0.0003,0.0017</t>
-  </si>
-  <si>
-    <t>0.9968,0.0003,0.0001,0.0024</t>
-  </si>
-  <si>
-    <t>0.9867,0.0107,0.0010,0.0028</t>
-  </si>
-  <si>
-    <t>0.9960,0.0020,0.0003,0.0011</t>
-  </si>
-  <si>
-    <t>0.9977,0.0004,0.0000,0.0014</t>
-  </si>
-  <si>
-    <t>0.9977,0.0008,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.4004,0.0202,0.7421,0.0038</t>
-  </si>
-  <si>
-    <t>0.0973,0.0285,0.9035,0.0022</t>
-  </si>
-  <si>
-    <t>0.6529,0.0138,0.4885,0.0005</t>
-  </si>
-  <si>
-    <t>0.1876,0.0183,0.8454,0.0100</t>
-  </si>
-  <si>
-    <t>0.7952,0.0223,0.2151,0.0079</t>
-  </si>
-  <si>
-    <t>0.0007,0.9981,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.9930,0.0012,0.0012</t>
-  </si>
-  <si>
-    <t>0.0686,0.9159,0.0059,0.0101</t>
-  </si>
-  <si>
-    <t>0.0024,0.9920,0.0032,0.0037</t>
-  </si>
-  <si>
-    <t>0.0017,0.9938,0.0038,0.0040</t>
-  </si>
-  <si>
-    <t>0.7675,0.0315,0.2284,0.0050</t>
-  </si>
-  <si>
-    <t>0.8269,0.0290,0.1444,0.0051</t>
-  </si>
-  <si>
-    <t>0.0057,0.0033,0.9769,0.0403</t>
-  </si>
-  <si>
-    <t>0.1580,0.0161,0.8563,0.0145</t>
-  </si>
-  <si>
-    <t>0.0234,0.0040,0.9730,0.0054</t>
-  </si>
-  <si>
-    <t>0.5551,0.0131,0.5777,0.0056</t>
-  </si>
-  <si>
-    <t>0.0050,0.0026,0.9899,0.0052</t>
-  </si>
-  <si>
-    <t>0.1654,0.8516,0.0096,0.0094</t>
-  </si>
-  <si>
-    <t>0.5540,0.1591,0.3258,0.0089</t>
-  </si>
-  <si>
-    <t>0.0031,0.0081,0.9889,0.0175</t>
-  </si>
-  <si>
-    <t>0.0174,0.9680,0.0079,0.0001</t>
-  </si>
-  <si>
-    <t>0.8817,0.0618,0.0457,0.0334</t>
-  </si>
-  <si>
-    <t>0.9209,0.0544,0.0192,0.0072</t>
-  </si>
-  <si>
-    <t>0.8605,0.2011,0.0064,0.0040</t>
-  </si>
-  <si>
-    <t>0.0253,0.9553,0.0671,0.0021</t>
-  </si>
-  <si>
-    <t>0.0132,0.9383,0.0291,0.0302</t>
-  </si>
-  <si>
-    <t>0.2441,0.0161,0.7981,0.0077</t>
-  </si>
-  <si>
-    <t>0.3774,0.0322,0.6964,0.0075</t>
-  </si>
-  <si>
-    <t>0.2563,0.0093,0.8272,0.0040</t>
-  </si>
-  <si>
-    <t>0.0437,0.0041,0.9650,0.0014</t>
-  </si>
-  <si>
-    <t>0.0011,0.9959,0.0026,0.0005</t>
-  </si>
-  <si>
-    <t>0.0306,0.0260,0.9547,0.0078</t>
-  </si>
-  <si>
-    <t>0.0529,0.1907,0.0019,0.9046</t>
-  </si>
-  <si>
-    <t>0.0011,0.9921,0.0019,0.0094</t>
-  </si>
-  <si>
-    <t>0.0007,0.9948,0.0236,0.0041</t>
-  </si>
-  <si>
-    <t>0.0002,0.9974,0.0060,0.0059</t>
-  </si>
-  <si>
-    <t>0.0313,0.0684,0.9268,0.0226</t>
-  </si>
-  <si>
-    <t>0.0028,0.8522,0.9761,0.0013</t>
-  </si>
-  <si>
-    <t>0.0696,0.0035,0.9535,0.0019</t>
-  </si>
-  <si>
-    <t>0.0026,0.0020,0.9942,0.0077</t>
-  </si>
-  <si>
-    <t>0.0127,0.0058,0.9782,0.0054</t>
-  </si>
-  <si>
-    <t>0.0084,0.3363,0.9284,0.0036</t>
-  </si>
-  <si>
-    <t>0.9909,0.0071,0.0003,0.0015</t>
-  </si>
-  <si>
-    <t>0.9732,0.0153,0.0097,0.0024</t>
-  </si>
-  <si>
-    <t>0.9737,0.0243,0.0050,0.0021</t>
-  </si>
-  <si>
-    <t>0.0046,0.0132,0.9839,0.0333</t>
-  </si>
-  <si>
-    <t>0.9915,0.0058,0.0013,0.0014</t>
-  </si>
-  <si>
-    <t>0.9956,0.0026,0.0004,0.0011</t>
-  </si>
-  <si>
-    <t>0.6778,0.4757,0.0037,0.0039</t>
-  </si>
-  <si>
-    <t>0.0039,0.9205,0.9651,0.0009</t>
-  </si>
-  <si>
-    <t>0.0143,0.3279,0.9546,0.0161</t>
-  </si>
-  <si>
-    <t>0.0156,0.2449,0.5651,0.1622</t>
-  </si>
-  <si>
-    <t>0.0033,0.9689,0.8874,0.0027</t>
-  </si>
-  <si>
-    <t>0.0122,0.0137,0.9772,0.0098</t>
-  </si>
-  <si>
-    <t>0.0120,0.9761,0.0205,0.0009</t>
-  </si>
-  <si>
-    <t>0.0041,0.9919,0.0036,0.0004</t>
-  </si>
-  <si>
-    <t>0.2422,0.0162,0.8505,0.0066</t>
-  </si>
-  <si>
-    <t>0.3799,0.0953,0.6662,0.0092</t>
-  </si>
-  <si>
-    <t>0.0487,0.0212,0.9477,0.0066</t>
-  </si>
-  <si>
-    <t>0.0072,0.9561,0.2764,0.0017</t>
-  </si>
-  <si>
-    <t>0.0044,0.9645,0.5524,0.0026</t>
-  </si>
-  <si>
-    <t>0.0016,0.9950,0.1539,0.0004</t>
-  </si>
-  <si>
-    <t>0.0011,0.9835,0.9228,0.0006</t>
-  </si>
-  <si>
-    <t>0.0070,0.0002,0.0012,0.9961</t>
-  </si>
-  <si>
-    <t>0.0025,0.0009,0.0004,0.9985</t>
-  </si>
-  <si>
-    <t>0.0038,0.0087,0.0003,0.9970</t>
-  </si>
-  <si>
-    <t>0.0249,0.0035,0.0023,0.9883</t>
-  </si>
-  <si>
-    <t>0.0049,0.0009,0.0011,0.9968</t>
-  </si>
-  <si>
-    <t>0.0154,0.0040,0.0002,0.9947</t>
-  </si>
-  <si>
-    <t>0.0013,0.9938,0.0562,0.0003</t>
-  </si>
-  <si>
-    <t>0.0026,0.9297,0.9611,0.0008</t>
-  </si>
-  <si>
-    <t>0.0146,0.8402,0.4548,0.0181</t>
-  </si>
-  <si>
-    <t>0.0044,0.9304,0.8031,0.0032</t>
-  </si>
-  <si>
-    <t>0.0011,0.9868,0.8383,0.0006</t>
-  </si>
-  <si>
-    <t>0.0032,0.9725,0.3055,0.0028</t>
-  </si>
-  <si>
-    <t>0.9962,0.0011,0.0003,0.0018</t>
-  </si>
-  <si>
-    <t>0.9911,0.0091,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.9862,0.0107,0.0009,0.0031</t>
-  </si>
-  <si>
-    <t>0.9879,0.0038,0.0010,0.0053</t>
-  </si>
-  <si>
-    <t>0.9657,0.0174,0.0043,0.0124</t>
-  </si>
-  <si>
-    <t>0.9959,0.0012,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.9934,0.0051,0.0006,0.0012</t>
-  </si>
-  <si>
-    <t>0.9939,0.0039,0.0011,0.0010</t>
-  </si>
-  <si>
-    <t>0.9945,0.0010,0.0003,0.0034</t>
-  </si>
-  <si>
-    <t>0.9935,0.0019,0.0018,0.0016</t>
-  </si>
-  <si>
-    <t>0.9923,0.0033,0.0004,0.0032</t>
-  </si>
-  <si>
-    <t>0.9968,0.0003,0.0001,0.0022</t>
-  </si>
-  <si>
-    <t>0.9979,0.0003,0.0001,0.0012</t>
-  </si>
-  <si>
-    <t>0.9948,0.0022,0.0009,0.0014</t>
-  </si>
-  <si>
-    <t>0.9939,0.0033,0.0007,0.0014</t>
-  </si>
-  <si>
-    <t>0.9973,0.0006,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.0123,0.0059,0.9800,0.0246</t>
-  </si>
-  <si>
-    <t>0.0452,0.0470,0.9401,0.0040</t>
-  </si>
-  <si>
-    <t>0.8749,0.0099,0.0817,0.0089</t>
-  </si>
-  <si>
-    <t>0.0119,0.0040,0.9874,0.0019</t>
-  </si>
-  <si>
-    <t>0.0170,0.9710,0.0033,0.0058</t>
-  </si>
-  <si>
-    <t>0.0022,0.9923,0.0010,0.0039</t>
-  </si>
-  <si>
-    <t>0.0043,0.9890,0.0011,0.0047</t>
-  </si>
-  <si>
-    <t>0.0696,0.9320,0.0050,0.0032</t>
-  </si>
-  <si>
-    <t>0.0049,0.9884,0.0012,0.0026</t>
-  </si>
-  <si>
-    <t>0.0027,0.9931,0.0022,0.0012</t>
-  </si>
-  <si>
-    <t>0.5898,0.5866,0.0023,0.0020</t>
-  </si>
-  <si>
-    <t>0.0427,0.9179,0.0377,0.0078</t>
-  </si>
-  <si>
-    <t>0.0731,0.0120,0.9146,0.0252</t>
-  </si>
-  <si>
-    <t>0.5212,0.0640,0.4174,0.0118</t>
-  </si>
-  <si>
-    <t>0.6825,0.0913,0.1906,0.0099</t>
-  </si>
-  <si>
-    <t>0.0201,0.0192,0.0068,0.9831</t>
-  </si>
-  <si>
-    <t>0.0010,0.9959,0.0024,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.9988,0.0012,0.0011</t>
-  </si>
-  <si>
-    <t>0.0051,0.9784,0.0109,0.0447</t>
-  </si>
-  <si>
-    <t>0.0024,0.9796,0.4287,0.0061</t>
-  </si>
-  <si>
-    <t>0.0107,0.9822,0.0188,0.0007</t>
-  </si>
-  <si>
-    <t>0.6755,0.4035,0.0328,0.0090</t>
-  </si>
-  <si>
-    <t>0.8519,0.1613,0.0194,0.0122</t>
-  </si>
-  <si>
-    <t>0.9911,0.0027,0.0013,0.0027</t>
-  </si>
-  <si>
-    <t>0.9963,0.0011,0.0002,0.0016</t>
-  </si>
-  <si>
-    <t>0.9932,0.0039,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.9975,0.0012,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9966,0.0006,0.0001,0.0022</t>
-  </si>
-  <si>
-    <t>0.9875,0.0076,0.0021,0.0016</t>
-  </si>
-  <si>
-    <t>0.9908,0.0041,0.0023,0.0017</t>
-  </si>
-  <si>
-    <t>0.9964,0.0016,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.0166,0.7522,0.7922,0.0103</t>
-  </si>
-  <si>
-    <t>0.0204,0.6373,0.6940,0.0033</t>
-  </si>
-  <si>
-    <t>0.0094,0.0560,0.9671,0.0089</t>
-  </si>
-  <si>
-    <t>0.0376,0.2216,0.8508,0.0053</t>
-  </si>
-  <si>
-    <t>0.9418,0.0116,0.0063,0.0300</t>
-  </si>
-  <si>
-    <t>0.8073,0.0146,0.2733,0.0028</t>
-  </si>
-  <si>
-    <t>0.2258,0.0048,0.8688,0.0037</t>
-  </si>
-  <si>
-    <t>0.7546,0.0288,0.2675,0.0110</t>
-  </si>
-  <si>
-    <t>0.0937,0.0006,0.0018,0.9696</t>
-  </si>
-  <si>
-    <t>0.0001,0.0020,0.0010,0.9994</t>
-  </si>
-  <si>
-    <t>0.0013,0.0011,0.0002,0.9992</t>
-  </si>
-  <si>
-    <t>0.0080,0.0001,0.0001,0.9980</t>
-  </si>
-  <si>
-    <t>0.0013,0.9795,0.7032,0.0028</t>
-  </si>
-  <si>
-    <t>0.9839,0.0056,0.0021,0.0060</t>
-  </si>
-  <si>
-    <t>0.0234,0.9563,0.0020,0.0150</t>
-  </si>
-  <si>
-    <t>0.9830,0.0063,0.0024,0.0064</t>
-  </si>
-  <si>
-    <t>0.2701,0.7568,0.0194,0.0241</t>
-  </si>
-  <si>
-    <t>0.9876,0.0043,0.0034,0.0021</t>
-  </si>
-  <si>
-    <t>0.6831,0.0060,0.0581,0.2615</t>
-  </si>
-  <si>
-    <t>0.9864,0.0023,0.0020,0.0071</t>
-  </si>
-  <si>
-    <t>0.0017,0.0057,0.9667,0.0727</t>
-  </si>
-  <si>
-    <t>0.9560,0.0019,0.0119,0.0292</t>
-  </si>
-  <si>
-    <t>0.9532,0.0023,0.0020,0.0462</t>
-  </si>
-  <si>
-    <t>0.4353,0.5968,0.0350,0.0174</t>
-  </si>
-  <si>
-    <t>0.9933,0.0022,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.9168,0.0254,0.0453,0.0045</t>
-  </si>
-  <si>
-    <t>0.1070,0.8461,0.0171,0.0327</t>
-  </si>
-  <si>
-    <t>0.8304,0.1126,0.0587,0.0308</t>
-  </si>
-  <si>
-    <t>0.8074,0.1369,0.0370,0.0172</t>
-  </si>
-  <si>
-    <t>0.9915,0.0024,0.0013,0.0037</t>
-  </si>
-  <si>
-    <t>0.9933,0.0018,0.0001,0.0042</t>
-  </si>
-  <si>
-    <t>0.9947,0.0026,0.0013,0.0011</t>
-  </si>
-  <si>
-    <t>0.9853,0.0005,0.0011,0.0147</t>
-  </si>
-  <si>
-    <t>0.9958,0.0007,0.0002,0.0027</t>
-  </si>
-  <si>
-    <t>0.9807,0.0130,0.0017,0.0049</t>
-  </si>
-  <si>
-    <t>0.9959,0.0012,0.0002,0.0017</t>
-  </si>
-  <si>
-    <t>0.9965,0.0007,0.0002,0.0020</t>
-  </si>
-  <si>
-    <t>0.4929,0.6829,0.0015,0.0017</t>
-  </si>
-  <si>
-    <t>0.6098,0.4741,0.0110,0.0065</t>
-  </si>
-  <si>
-    <t>0.5000,0.6008,0.0106,0.0059</t>
-  </si>
-  <si>
-    <t>0.0156,0.0602,0.9870,0.0022</t>
-  </si>
-  <si>
-    <t>0.9352,0.0769,0.0050,0.0040</t>
-  </si>
-  <si>
-    <t>0.9676,0.0275,0.0053,0.0037</t>
-  </si>
-  <si>
-    <t>0.9730,0.0235,0.0034,0.0030</t>
-  </si>
-  <si>
-    <t>0.9817,0.0171,0.0018,0.0026</t>
-  </si>
-  <si>
-    <t>0.0021,0.0174,0.9967,0.0015</t>
-  </si>
-  <si>
-    <t>0.9427,0.0530,0.0043,0.0082</t>
-  </si>
-  <si>
-    <t>0.0032,0.0036,0.9903,0.0051</t>
-  </si>
-  <si>
-    <t>0.0070,0.2275,0.9165,0.0146</t>
-  </si>
-  <si>
-    <t>0.0023,0.0087,0.9925,0.0049</t>
-  </si>
-  <si>
-    <t>0.0520,0.2621,0.8152,0.0141</t>
-  </si>
-  <si>
-    <t>0.0037,0.0093,0.9845,0.0122</t>
-  </si>
-  <si>
-    <t>0.0036,0.0010,0.9932,0.0018</t>
-  </si>
-  <si>
-    <t>0.0280,0.0326,0.9551,0.0100</t>
-  </si>
-  <si>
-    <t>0.0400,0.0124,0.9371,0.0168</t>
-  </si>
-  <si>
-    <t>0.1334,0.0179,0.8950,0.0048</t>
-  </si>
-  <si>
-    <t>0.1027,0.6322,0.1772,0.0849</t>
-  </si>
-  <si>
-    <t>0.3563,0.0791,0.5601,0.0038</t>
-  </si>
-  <si>
-    <t>0.2128,0.1384,0.7317,0.0056</t>
-  </si>
-  <si>
-    <t>0.3165,0.0306,0.7535,0.0031</t>
-  </si>
-  <si>
-    <t>0.7405,0.0302,0.3137,0.0069</t>
-  </si>
-  <si>
-    <t>0.3049,0.0326,0.7654,0.0062</t>
-  </si>
-  <si>
-    <t>0.7431,0.4055,0.0035,0.0033</t>
-  </si>
-  <si>
-    <t>0.2819,0.7625,0.0051,0.0071</t>
-  </si>
-  <si>
-    <t>0.2753,0.8334,0.0047,0.0009</t>
-  </si>
-  <si>
-    <t>0.6232,0.4793,0.0032,0.0055</t>
-  </si>
-  <si>
-    <t>0.4135,0.6993,0.0095,0.0060</t>
-  </si>
-  <si>
-    <t>0.9338,0.0175,0.0175,0.0026</t>
-  </si>
-  <si>
-    <t>0.9220,0.0028,0.1412,0.0003</t>
-  </si>
-  <si>
-    <t>0.8751,0.0143,0.0970,0.0064</t>
-  </si>
-  <si>
-    <t>0.7580,0.0160,0.2735,0.0087</t>
-  </si>
-  <si>
-    <t>0.5637,0.0101,0.4915,0.0145</t>
-  </si>
-  <si>
-    <t>0.0036,0.0047,0.9840,0.0369</t>
-  </si>
-  <si>
-    <t>0.0255,0.1829,0.4273,0.3551</t>
-  </si>
-  <si>
-    <t>0.0190,0.0126,0.9747,0.0029</t>
-  </si>
-  <si>
-    <t>0.1331,0.5273,0.3676,0.1288</t>
-  </si>
-  <si>
-    <t>0.0549,0.1482,0.7083,0.0218</t>
-  </si>
-  <si>
-    <t>0.9924,0.0045,0.0004,0.0023</t>
-  </si>
-  <si>
-    <t>0.9887,0.0071,0.0022,0.0015</t>
-  </si>
-  <si>
-    <t>0.9837,0.0072,0.0024,0.0047</t>
-  </si>
-  <si>
-    <t>0.9946,0.0032,0.0016,0.0006</t>
-  </si>
-  <si>
-    <t>0.9667,0.0252,0.0080,0.0035</t>
-  </si>
-  <si>
-    <t>0.9884,0.0079,0.0015,0.0031</t>
-  </si>
-  <si>
-    <t>0.9886,0.0094,0.0012,0.0021</t>
-  </si>
-  <si>
-    <t>0.9977,0.0004,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.0053,0.0230,0.9936,0.0020</t>
-  </si>
-  <si>
-    <t>0.3870,0.3489,0.4097,0.0936</t>
-  </si>
-  <si>
-    <t>0.7643,0.0795,0.0533,0.0745</t>
-  </si>
-  <si>
-    <t>0.0076,0.0883,0.9803,0.0026</t>
-  </si>
-  <si>
-    <t>0.0050,0.0091,0.9787,0.0112</t>
-  </si>
-  <si>
-    <t>0.0196,0.0553,0.9431,0.0147</t>
-  </si>
-  <si>
-    <t>0.0073,0.0078,0.9893,0.0085</t>
-  </si>
-  <si>
-    <t>0.0748,0.0146,0.8987,0.0098</t>
-  </si>
-  <si>
-    <t>0.0101,0.0055,0.9852,0.0041</t>
-  </si>
-  <si>
-    <t>0.0376,0.0705,0.7494,0.1452</t>
-  </si>
-  <si>
-    <t>0.0149,0.0614,0.9256,0.0294</t>
-  </si>
-  <si>
-    <t>0.8797,0.0181,0.0726,0.0081</t>
-  </si>
-  <si>
-    <t>0.6654,0.0275,0.4019,0.0099</t>
-  </si>
-  <si>
-    <t>0.8018,0.0571,0.0955,0.0238</t>
-  </si>
-  <si>
-    <t>0.9872,0.0153,0.0005,0.0017</t>
-  </si>
-  <si>
-    <t>0.9918,0.0057,0.0010,0.0013</t>
-  </si>
-  <si>
-    <t>0.9910,0.0053,0.0007,0.0030</t>
-  </si>
-  <si>
-    <t>0.9882,0.0061,0.0013,0.0041</t>
-  </si>
-  <si>
-    <t>0.9754,0.0051,0.0037,0.0129</t>
-  </si>
-  <si>
-    <t>0.9954,0.0020,0.0004,0.0015</t>
-  </si>
-  <si>
-    <t>0.9927,0.0034,0.0005,0.0022</t>
-  </si>
-  <si>
-    <t>0.9949,0.0025,0.0002,0.0024</t>
-  </si>
-  <si>
-    <t>0.0059,0.0884,0.9706,0.0066</t>
-  </si>
-  <si>
-    <t>0.0143,0.1024,0.9543,0.0039</t>
-  </si>
-  <si>
-    <t>0.0159,0.3710,0.8054,0.0223</t>
-  </si>
-  <si>
-    <t>0.0178,0.0119,0.9724,0.0007</t>
-  </si>
-  <si>
-    <t>0.0260,0.0031,0.9759,0.0026</t>
-  </si>
-  <si>
-    <t>0.4281,0.0042,0.5773,0.0304</t>
-  </si>
-  <si>
-    <t>0.6083,0.0879,0.2822,0.0185</t>
-  </si>
-  <si>
-    <t>0.1304,0.0017,0.4073,0.2099</t>
-  </si>
-  <si>
-    <t>0.9728,0.0004,0.0006,0.0381</t>
-  </si>
-  <si>
-    <t>0.0244,0.0078,0.0017,0.9878</t>
-  </si>
-  <si>
-    <t>0.0484,0.0012,0.0007,0.9856</t>
-  </si>
-  <si>
-    <t>0.0030,0.0003,0.0012,0.9979</t>
-  </si>
-  <si>
-    <t>0.0004,0.0018,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.7483,0.0337,0.1177,0.1076</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9669,0.0079,0.0042,0.0094</t>
+  </si>
+  <si>
+    <t>0.0059,0.0003,0.0004,0.9976</t>
+  </si>
+  <si>
+    <t>0.9137,0.0055,0.0016,0.1353</t>
+  </si>
+  <si>
+    <t>0.0777,0.0032,0.0023,0.9718</t>
+  </si>
+  <si>
+    <t>0.9952,0.0007,0.0003,0.0029</t>
+  </si>
+  <si>
+    <t>0.9940,0.0011,0.0001,0.0040</t>
+  </si>
+  <si>
+    <t>0.9924,0.0017,0.0005,0.0042</t>
+  </si>
+  <si>
+    <t>0.9949,0.0006,0.0001,0.0039</t>
+  </si>
+  <si>
+    <t>0.9897,0.0090,0.0012,0.0018</t>
+  </si>
+  <si>
+    <t>0.9947,0.0028,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9954,0.0034,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9961,0.0008,0.0002,0.0019</t>
+  </si>
+  <si>
+    <t>0.8687,0.0114,0.1509,0.0021</t>
+  </si>
+  <si>
+    <t>0.3466,0.0521,0.7029,0.0119</t>
+  </si>
+  <si>
+    <t>0.1492,0.0526,0.8187,0.0016</t>
+  </si>
+  <si>
+    <t>0.0055,0.0043,0.9825,0.0237</t>
+  </si>
+  <si>
+    <t>0.9166,0.0065,0.1070,0.0013</t>
+  </si>
+  <si>
+    <t>0.0011,0.9963,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.0063,0.9859,0.0028,0.0018</t>
+  </si>
+  <si>
+    <t>0.0635,0.9310,0.0031,0.0049</t>
+  </si>
+  <si>
+    <t>0.0029,0.9907,0.0018,0.0043</t>
+  </si>
+  <si>
+    <t>0.0046,0.9900,0.0020,0.0017</t>
+  </si>
+  <si>
+    <t>0.9324,0.0012,0.1144,0.0013</t>
+  </si>
+  <si>
+    <t>0.7936,0.0502,0.1524,0.0105</t>
+  </si>
+  <si>
+    <t>0.0322,0.0025,0.9586,0.0141</t>
+  </si>
+  <si>
+    <t>0.0167,0.0429,0.9231,0.0127</t>
+  </si>
+  <si>
+    <t>0.1387,0.0167,0.8829,0.0048</t>
+  </si>
+  <si>
+    <t>0.1666,0.0145,0.8376,0.0136</t>
+  </si>
+  <si>
+    <t>0.0204,0.0017,0.9744,0.0036</t>
+  </si>
+  <si>
+    <t>0.2524,0.8044,0.0102,0.0045</t>
+  </si>
+  <si>
+    <t>0.4969,0.4727,0.0619,0.0294</t>
+  </si>
+  <si>
+    <t>0.0105,0.0165,0.9828,0.0056</t>
+  </si>
+  <si>
+    <t>0.0053,0.9737,0.0244,0.0001</t>
+  </si>
+  <si>
+    <t>0.6364,0.2770,0.0294,0.0764</t>
+  </si>
+  <si>
+    <t>0.4736,0.0861,0.4876,0.0288</t>
+  </si>
+  <si>
+    <t>0.7864,0.2833,0.0192,0.0031</t>
+  </si>
+  <si>
+    <t>0.0391,0.9380,0.0627,0.0043</t>
+  </si>
+  <si>
+    <t>0.0094,0.9415,0.0744,0.0266</t>
+  </si>
+  <si>
+    <t>0.1652,0.0245,0.8716,0.0095</t>
+  </si>
+  <si>
+    <t>0.0988,0.0376,0.8833,0.0097</t>
+  </si>
+  <si>
+    <t>0.2307,0.0051,0.7890,0.0124</t>
+  </si>
+  <si>
+    <t>0.0267,0.6704,0.8375,0.0135</t>
+  </si>
+  <si>
+    <t>0.0047,0.9816,0.0076,0.0095</t>
+  </si>
+  <si>
+    <t>0.0079,0.0091,0.9806,0.0070</t>
+  </si>
+  <si>
+    <t>0.0279,0.6701,0.0044,0.7717</t>
+  </si>
+  <si>
+    <t>0.0002,0.9958,0.0010,0.0189</t>
+  </si>
+  <si>
+    <t>0.0006,0.9957,0.0068,0.0008</t>
+  </si>
+  <si>
+    <t>0.0004,0.9957,0.0109,0.0077</t>
+  </si>
+  <si>
+    <t>0.0104,0.0876,0.9265,0.0275</t>
+  </si>
+  <si>
+    <t>0.0291,0.6427,0.7972,0.0151</t>
+  </si>
+  <si>
+    <t>0.0377,0.0064,0.9562,0.0095</t>
+  </si>
+  <si>
+    <t>0.0059,0.0013,0.9907,0.0028</t>
+  </si>
+  <si>
+    <t>0.0710,0.0090,0.9167,0.0160</t>
+  </si>
+  <si>
+    <t>0.0069,0.0588,0.9710,0.0075</t>
+  </si>
+  <si>
+    <t>0.9706,0.0305,0.0011,0.0053</t>
+  </si>
+  <si>
+    <t>0.9624,0.0215,0.0117,0.0021</t>
+  </si>
+  <si>
+    <t>0.9679,0.0100,0.0095,0.0162</t>
+  </si>
+  <si>
+    <t>0.0166,0.0411,0.9628,0.0163</t>
+  </si>
+  <si>
+    <t>0.9933,0.0026,0.0004,0.0029</t>
+  </si>
+  <si>
+    <t>0.9906,0.0069,0.0013,0.0017</t>
+  </si>
+  <si>
+    <t>0.9675,0.0643,0.0010,0.0015</t>
+  </si>
+  <si>
+    <t>0.0036,0.9302,0.9347,0.0016</t>
+  </si>
+  <si>
+    <t>0.0546,0.0453,0.9290,0.0193</t>
+  </si>
+  <si>
+    <t>0.0312,0.0548,0.9236,0.0207</t>
+  </si>
+  <si>
+    <t>0.0020,0.9480,0.9602,0.0014</t>
+  </si>
+  <si>
+    <t>0.0033,0.0194,0.9897,0.0101</t>
+  </si>
+  <si>
+    <t>0.0367,0.9532,0.0245,0.0013</t>
+  </si>
+  <si>
+    <t>0.0054,0.9922,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.4600,0.0104,0.7658,0.0026</t>
+  </si>
+  <si>
+    <t>0.2384,0.0469,0.8124,0.0273</t>
+  </si>
+  <si>
+    <t>0.0384,0.0305,0.9284,0.0439</t>
+  </si>
+  <si>
+    <t>0.0065,0.9125,0.8448,0.0021</t>
+  </si>
+  <si>
+    <t>0.0019,0.9820,0.3564,0.0013</t>
+  </si>
+  <si>
+    <t>0.0017,0.9944,0.1015,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.9958,0.8939,0.0003</t>
+  </si>
+  <si>
+    <t>0.0031,0.0007,0.0106,0.9954</t>
+  </si>
+  <si>
+    <t>0.0013,0.0011,0.0003,0.9991</t>
+  </si>
+  <si>
+    <t>0.0066,0.0024,0.0006,0.9969</t>
+  </si>
+  <si>
+    <t>0.0108,0.0016,0.0008,0.9954</t>
+  </si>
+  <si>
+    <t>0.0030,0.0016,0.0006,0.9979</t>
+  </si>
+  <si>
+    <t>0.0079,0.0023,0.0009,0.9959</t>
+  </si>
+  <si>
+    <t>0.0038,0.9770,0.3658,0.0023</t>
+  </si>
+  <si>
+    <t>0.0038,0.9593,0.9165,0.0018</t>
+  </si>
+  <si>
+    <t>0.0202,0.8371,0.2241,0.0321</t>
+  </si>
+  <si>
+    <t>0.0018,0.9292,0.9526,0.0026</t>
+  </si>
+  <si>
+    <t>0.0004,0.9929,0.9434,0.0002</t>
+  </si>
+  <si>
+    <t>0.0034,0.9491,0.5058,0.0017</t>
+  </si>
+  <si>
+    <t>0.9926,0.0029,0.0003,0.0040</t>
+  </si>
+  <si>
+    <t>0.9863,0.0098,0.0025,0.0023</t>
+  </si>
+  <si>
+    <t>0.9843,0.0138,0.0018,0.0016</t>
+  </si>
+  <si>
+    <t>0.9853,0.0144,0.0009,0.0026</t>
+  </si>
+  <si>
+    <t>0.9928,0.0069,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9955,0.0010,0.0003,0.0021</t>
+  </si>
+  <si>
+    <t>0.9973,0.0007,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9916,0.0047,0.0006,0.0028</t>
+  </si>
+  <si>
+    <t>0.9895,0.0035,0.0012,0.0061</t>
+  </si>
+  <si>
+    <t>0.9956,0.0011,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9977,0.0005,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9878,0.0008,0.0005,0.0141</t>
+  </si>
+  <si>
+    <t>0.9957,0.0012,0.0004,0.0019</t>
+  </si>
+  <si>
+    <t>0.9872,0.0087,0.0032,0.0017</t>
+  </si>
+  <si>
+    <t>0.9971,0.0006,0.0002,0.0018</t>
+  </si>
+  <si>
+    <t>0.9971,0.0005,0.0001,0.0019</t>
+  </si>
+  <si>
+    <t>0.0029,0.0053,0.9952,0.0035</t>
+  </si>
+  <si>
+    <t>0.0212,0.0079,0.9681,0.0073</t>
+  </si>
+  <si>
+    <t>0.9765,0.0024,0.0081,0.0023</t>
+  </si>
+  <si>
+    <t>0.0122,0.0017,0.9842,0.0064</t>
+  </si>
+  <si>
+    <t>0.0076,0.9860,0.0014,0.0020</t>
+  </si>
+  <si>
+    <t>0.0114,0.9851,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.0121,0.9774,0.0012,0.0065</t>
+  </si>
+  <si>
+    <t>0.0137,0.9767,0.0022,0.0034</t>
+  </si>
+  <si>
+    <t>0.0018,0.9940,0.0009,0.0021</t>
+  </si>
+  <si>
+    <t>0.0085,0.9857,0.0068,0.0008</t>
+  </si>
+  <si>
+    <t>0.1765,0.8612,0.0040,0.0061</t>
+  </si>
+  <si>
+    <t>0.5532,0.2061,0.1099,0.1788</t>
+  </si>
+  <si>
+    <t>0.1412,0.0131,0.8751,0.0107</t>
+  </si>
+  <si>
+    <t>0.5826,0.0991,0.2867,0.0399</t>
+  </si>
+  <si>
+    <t>0.5766,0.0230,0.5506,0.0111</t>
+  </si>
+  <si>
+    <t>0.0422,0.0339,0.0035,0.9651</t>
+  </si>
+  <si>
+    <t>0.0008,0.9966,0.0044,0.0008</t>
+  </si>
+  <si>
+    <t>0.0005,0.9966,0.0032,0.0024</t>
+  </si>
+  <si>
+    <t>0.0019,0.9916,0.0015,0.0134</t>
+  </si>
+  <si>
+    <t>0.0032,0.9624,0.8479,0.0052</t>
+  </si>
+  <si>
+    <t>0.0185,0.9747,0.0179,0.0011</t>
+  </si>
+  <si>
+    <t>0.6644,0.3817,0.0740,0.0161</t>
+  </si>
+  <si>
+    <t>0.7989,0.2392,0.0162,0.0114</t>
+  </si>
+  <si>
+    <t>0.9749,0.0202,0.0026,0.0043</t>
+  </si>
+  <si>
+    <t>0.9955,0.0018,0.0005,0.0013</t>
+  </si>
+  <si>
+    <t>0.9944,0.0034,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.9917,0.0033,0.0015,0.0013</t>
+  </si>
+  <si>
+    <t>0.9954,0.0008,0.0001,0.0027</t>
+  </si>
+  <si>
+    <t>0.9819,0.0086,0.0055,0.0022</t>
+  </si>
+  <si>
+    <t>0.9859,0.0103,0.0021,0.0021</t>
+  </si>
+  <si>
+    <t>0.9956,0.0013,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.0176,0.8335,0.7226,0.0090</t>
+  </si>
+  <si>
+    <t>0.0172,0.7579,0.7335,0.0074</t>
+  </si>
+  <si>
+    <t>0.0157,0.0696,0.9657,0.0055</t>
+  </si>
+  <si>
+    <t>0.0092,0.1430,0.9741,0.0010</t>
+  </si>
+  <si>
+    <t>0.9830,0.0033,0.0057,0.0008</t>
+  </si>
+  <si>
+    <t>0.8528,0.0292,0.1089,0.0146</t>
+  </si>
+  <si>
+    <t>0.1424,0.0042,0.9306,0.0013</t>
+  </si>
+  <si>
+    <t>0.7894,0.0370,0.1320,0.0052</t>
+  </si>
+  <si>
+    <t>0.0833,0.0008,0.0007,0.9781</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.0020,0.0124,0.0006,0.9976</t>
+  </si>
+  <si>
+    <t>0.0067,0.0004,0.0011,0.9963</t>
+  </si>
+  <si>
+    <t>0.0029,0.9814,0.2747,0.0031</t>
+  </si>
+  <si>
+    <t>0.9856,0.0037,0.0006,0.0090</t>
+  </si>
+  <si>
+    <t>0.3488,0.7664,0.0017,0.0048</t>
+  </si>
+  <si>
+    <t>0.9966,0.0013,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.7773,0.3174,0.0083,0.0045</t>
+  </si>
+  <si>
+    <t>0.9798,0.0035,0.0115,0.0026</t>
+  </si>
+  <si>
+    <t>0.6583,0.0043,0.0156,0.4793</t>
+  </si>
+  <si>
+    <t>0.9826,0.0038,0.0034,0.0080</t>
+  </si>
+  <si>
+    <t>0.0072,0.0071,0.9646,0.0346</t>
+  </si>
+  <si>
+    <t>0.7495,0.0044,0.0360,0.2338</t>
+  </si>
+  <si>
+    <t>0.7755,0.0023,0.0098,0.3046</t>
+  </si>
+  <si>
+    <t>0.8250,0.2381,0.0193,0.0043</t>
+  </si>
+  <si>
+    <t>0.9750,0.0086,0.0070,0.0014</t>
+  </si>
+  <si>
+    <t>0.9485,0.0202,0.0162,0.0044</t>
+  </si>
+  <si>
+    <t>0.2776,0.6803,0.0469,0.0300</t>
+  </si>
+  <si>
+    <t>0.3999,0.0534,0.6868,0.0097</t>
+  </si>
+  <si>
+    <t>0.9048,0.0936,0.0114,0.0031</t>
+  </si>
+  <si>
+    <t>0.9915,0.0021,0.0003,0.0058</t>
+  </si>
+  <si>
+    <t>0.9902,0.0011,0.0003,0.0099</t>
+  </si>
+  <si>
+    <t>0.9949,0.0014,0.0005,0.0024</t>
+  </si>
+  <si>
+    <t>0.9914,0.0010,0.0002,0.0084</t>
+  </si>
+  <si>
+    <t>0.9969,0.0004,0.0001,0.0017</t>
+  </si>
+  <si>
+    <t>0.9953,0.0021,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9945,0.0016,0.0008,0.0018</t>
+  </si>
+  <si>
+    <t>0.9902,0.0036,0.0039,0.0021</t>
+  </si>
+  <si>
+    <t>0.8823,0.1778,0.0048,0.0013</t>
+  </si>
+  <si>
+    <t>0.5977,0.5864,0.0028,0.0030</t>
+  </si>
+  <si>
+    <t>0.3341,0.7592,0.0102,0.0047</t>
+  </si>
+  <si>
+    <t>0.0799,0.0478,0.9523,0.0028</t>
+  </si>
+  <si>
+    <t>0.9848,0.0083,0.0004,0.0038</t>
+  </si>
+  <si>
+    <t>0.9298,0.0642,0.0182,0.0031</t>
+  </si>
+  <si>
+    <t>0.9455,0.0475,0.0084,0.0093</t>
+  </si>
+  <si>
+    <t>0.9701,0.0360,0.0015,0.0039</t>
+  </si>
+  <si>
+    <t>0.0028,0.0410,0.9961,0.0011</t>
+  </si>
+  <si>
+    <t>0.9468,0.0492,0.0021,0.0085</t>
+  </si>
+  <si>
+    <t>0.0027,0.0052,0.9946,0.0020</t>
+  </si>
+  <si>
+    <t>0.0078,0.2863,0.9561,0.0219</t>
+  </si>
+  <si>
+    <t>0.0158,0.0110,0.9794,0.0031</t>
+  </si>
+  <si>
+    <t>0.0381,0.3920,0.9171,0.0084</t>
+  </si>
+  <si>
+    <t>0.0064,0.0140,0.9780,0.0208</t>
+  </si>
+  <si>
+    <t>0.0048,0.0035,0.9867,0.0094</t>
+  </si>
+  <si>
+    <t>0.0141,0.1032,0.9634,0.0185</t>
+  </si>
+  <si>
+    <t>0.1373,0.0179,0.8843,0.0107</t>
+  </si>
+  <si>
+    <t>0.1343,0.0321,0.8831,0.0078</t>
+  </si>
+  <si>
+    <t>0.4667,0.0589,0.5564,0.0174</t>
+  </si>
+  <si>
+    <t>0.0987,0.1780,0.6495,0.0047</t>
+  </si>
+  <si>
+    <t>0.0593,0.7679,0.1851,0.0060</t>
+  </si>
+  <si>
+    <t>0.5584,0.2413,0.1287,0.0655</t>
+  </si>
+  <si>
+    <t>0.6495,0.0867,0.2921,0.0240</t>
+  </si>
+  <si>
+    <t>0.5197,0.0338,0.5513,0.0144</t>
+  </si>
+  <si>
+    <t>0.7895,0.3849,0.0021,0.0018</t>
+  </si>
+  <si>
+    <t>0.0871,0.9299,0.0022,0.0032</t>
+  </si>
+  <si>
+    <t>0.4667,0.6526,0.0095,0.0038</t>
+  </si>
+  <si>
+    <t>0.9686,0.0342,0.0012,0.0050</t>
+  </si>
+  <si>
+    <t>0.9227,0.1062,0.0033,0.0053</t>
+  </si>
+  <si>
+    <t>0.6826,0.1131,0.1094,0.0346</t>
+  </si>
+  <si>
+    <t>0.9140,0.0066,0.0857,0.0011</t>
+  </si>
+  <si>
+    <t>0.9433,0.0088,0.0159,0.0081</t>
+  </si>
+  <si>
+    <t>0.7437,0.0223,0.2664,0.0086</t>
+  </si>
+  <si>
+    <t>0.4567,0.0605,0.5731,0.0083</t>
+  </si>
+  <si>
+    <t>0.0018,0.0124,0.9839,0.0869</t>
+  </si>
+  <si>
+    <t>0.0340,0.0829,0.8571,0.0749</t>
+  </si>
+  <si>
+    <t>0.0756,0.1431,0.8497,0.0113</t>
+  </si>
+  <si>
+    <t>0.2271,0.0790,0.6640,0.0420</t>
+  </si>
+  <si>
+    <t>0.1255,0.3785,0.5152,0.0079</t>
+  </si>
+  <si>
+    <t>0.9942,0.0022,0.0004,0.0024</t>
+  </si>
+  <si>
+    <t>0.9965,0.0013,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9877,0.0081,0.0015,0.0033</t>
+  </si>
+  <si>
+    <t>0.9967,0.0007,0.0002,0.0016</t>
+  </si>
+  <si>
+    <t>0.9859,0.0062,0.0009,0.0048</t>
+  </si>
+  <si>
+    <t>0.9883,0.0025,0.0003,0.0100</t>
+  </si>
+  <si>
+    <t>0.9821,0.0074,0.0024,0.0078</t>
+  </si>
+  <si>
+    <t>0.9967,0.0009,0.0001,0.0017</t>
+  </si>
+  <si>
+    <t>0.0161,0.0174,0.9805,0.0052</t>
+  </si>
+  <si>
+    <t>0.3650,0.3356,0.4123,0.0296</t>
+  </si>
+  <si>
+    <t>0.7488,0.0101,0.0606,0.1134</t>
+  </si>
+  <si>
+    <t>0.0255,0.0058,0.9798,0.0016</t>
+  </si>
+  <si>
+    <t>0.0032,0.0031,0.9855,0.0106</t>
+  </si>
+  <si>
+    <t>0.0235,0.0354,0.9589,0.0061</t>
+  </si>
+  <si>
+    <t>0.0052,0.0207,0.9947,0.0013</t>
+  </si>
+  <si>
+    <t>0.0950,0.0150,0.8971,0.0169</t>
+  </si>
+  <si>
+    <t>0.0033,0.0135,0.9903,0.0070</t>
+  </si>
+  <si>
+    <t>0.0060,0.0464,0.9057,0.0614</t>
+  </si>
+  <si>
+    <t>0.0627,0.3192,0.6547,0.0122</t>
+  </si>
+  <si>
+    <t>0.9564,0.0052,0.0222,0.0035</t>
+  </si>
+  <si>
+    <t>0.7308,0.0136,0.3893,0.0041</t>
+  </si>
+  <si>
+    <t>0.8338,0.0213,0.1395,0.0186</t>
+  </si>
+  <si>
+    <t>0.9252,0.0822,0.0048,0.0082</t>
+  </si>
+  <si>
+    <t>0.9931,0.0036,0.0005,0.0014</t>
+  </si>
+  <si>
+    <t>0.9959,0.0014,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.9924,0.0042,0.0014,0.0021</t>
+  </si>
+  <si>
+    <t>0.9878,0.0035,0.0007,0.0079</t>
+  </si>
+  <si>
+    <t>0.9955,0.0027,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9934,0.0052,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9891,0.0023,0.0003,0.0084</t>
+  </si>
+  <si>
+    <t>0.0257,0.1487,0.7947,0.0222</t>
+  </si>
+  <si>
+    <t>0.0029,0.0861,0.9844,0.0023</t>
+  </si>
+  <si>
+    <t>0.0200,0.0860,0.9139,0.0140</t>
+  </si>
+  <si>
+    <t>0.0499,0.0676,0.8425,0.0020</t>
+  </si>
+  <si>
+    <t>0.0561,0.0059,0.9163,0.0155</t>
+  </si>
+  <si>
+    <t>0.0428,0.0695,0.7996,0.2742</t>
+  </si>
+  <si>
+    <t>0.3214,0.0552,0.7028,0.0120</t>
+  </si>
+  <si>
+    <t>0.0911,0.0366,0.8630,0.0496</t>
+  </si>
+  <si>
+    <t>0.9240,0.0035,0.0038,0.0901</t>
+  </si>
+  <si>
+    <t>0.0261,0.0246,0.0107,0.9795</t>
+  </si>
+  <si>
+    <t>0.2472,0.0006,0.0003,0.9381</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.0003,0.9993</t>
+  </si>
+  <si>
+    <t>0.0038,0.0004,0.0002,0.9986</t>
+  </si>
+  <si>
+    <t>0.8862,0.0152,0.0312,0.0520</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2133,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2161,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2276,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2290,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2374,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2539,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2654,7 @@
         <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2920,7 @@
         <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2934,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2959,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2973,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3102,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3130,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3144,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3550,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3561,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3673,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4009,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4065,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4208,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4219,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4390,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4404,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4642,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4726,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4740,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4765,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4824,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4863,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4891,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5412,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5423,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5437,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
